--- a/Fiche de mouvement _04-2026.xlsx
+++ b/Fiche de mouvement _04-2026.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FDC6B9F-1F21-48F9-AC05-AF074B5FC7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{2FDC6B9F-1F21-48F9-AC05-AF074B5FC7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1BD278A-0F48-436D-BF30-6913C9093799}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EB61CAA8-C9F0-46A0-A741-29F004216494}"/>
   </bookViews>
   <sheets>
-    <sheet name="Douanes Oran-Exterieur" sheetId="1" r:id="rId1"/>
-    <sheet name="Douanes Oran-Port" sheetId="2" r:id="rId2"/>
+    <sheet name="DASHBOARD" sheetId="3" r:id="rId1"/>
+    <sheet name="Douanes Oran-Exterieur" sheetId="1" r:id="rId2"/>
+    <sheet name="Douanes Oran-Port" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="181">
   <si>
     <t>FICHE DE MOUVEMENT</t>
   </si>
@@ -150,510 +151,6 @@
     <t>26A0033000322ICS-0071</t>
   </si>
   <si>
-    <t>26A0005000037ICS-0142</t>
-  </si>
-  <si>
-    <t>26A0033000356ICS-0105</t>
-  </si>
-  <si>
-    <t>26A0003000380ICS-0031</t>
-  </si>
-  <si>
-    <t>26A0005000041ICS-0062</t>
-  </si>
-  <si>
-    <t>26A0055000129ICS-0283</t>
-  </si>
-  <si>
-    <t>26A0010000094ICS-0079</t>
-  </si>
-  <si>
-    <t>26A0005000041ICS-0055</t>
-  </si>
-  <si>
-    <t>26A0005000041ICS-0032</t>
-  </si>
-  <si>
-    <t>26A001000081ICS-0123</t>
-  </si>
-  <si>
-    <t>26A0010000085ICS-0014</t>
-  </si>
-  <si>
-    <t>26A0010000100ICS-0090</t>
-  </si>
-  <si>
-    <t>26A0005000054ICS-0010</t>
-  </si>
-  <si>
-    <t>MEDU7035758</t>
-  </si>
-  <si>
-    <t>MSMU6012495</t>
-  </si>
-  <si>
-    <t>MSMU6629152</t>
-  </si>
-  <si>
-    <t>AMCU8006348</t>
-  </si>
-  <si>
-    <t>AMCU8010230</t>
-  </si>
-  <si>
-    <t>TCLU4815545</t>
-  </si>
-  <si>
-    <t>TLLU1674879</t>
-  </si>
-  <si>
-    <t>FSCU8731485</t>
-  </si>
-  <si>
-    <t>TCNU3380168</t>
-  </si>
-  <si>
-    <t>CMAU7892562</t>
-  </si>
-  <si>
-    <t>MEDU6232541</t>
-  </si>
-  <si>
-    <t>MSCU5366405</t>
-  </si>
-  <si>
-    <t>MSCU5462374</t>
-  </si>
-  <si>
-    <t>MSDU8594341</t>
-  </si>
-  <si>
-    <t>TRHU5080250</t>
-  </si>
-  <si>
-    <t>TRHU8732250</t>
-  </si>
-  <si>
-    <t>CMAU9654943</t>
-  </si>
-  <si>
-    <t>HASU4929166</t>
-  </si>
-  <si>
-    <t>HASU51567468</t>
-  </si>
-  <si>
-    <t>MRSU6980064</t>
-  </si>
-  <si>
-    <t>PONU8049086</t>
-  </si>
-  <si>
-    <t>TLLU8054381</t>
-  </si>
-  <si>
-    <t>APZU2133059</t>
-  </si>
-  <si>
-    <t>CMAU1942080</t>
-  </si>
-  <si>
-    <t>TEMU3871541</t>
-  </si>
-  <si>
-    <t>HASU5124253</t>
-  </si>
-  <si>
-    <t>MRKU7147471</t>
-  </si>
-  <si>
-    <t>MRKU7767600</t>
-  </si>
-  <si>
-    <t>MRKU8623042</t>
-  </si>
-  <si>
-    <t>MSKU5610064</t>
-  </si>
-  <si>
-    <t>SUDU7471450</t>
-  </si>
-  <si>
-    <t>TCKU3020779</t>
-  </si>
-  <si>
-    <t>TEMU3420018</t>
-  </si>
-  <si>
-    <t>HASU1480370</t>
-  </si>
-  <si>
-    <t>TCLU7176772</t>
-  </si>
-  <si>
-    <t>ARKU2411320</t>
-  </si>
-  <si>
-    <t>TRHU3074161</t>
-  </si>
-  <si>
-    <t>KOCU4511319</t>
-  </si>
-  <si>
-    <t>TLLU6022552</t>
-  </si>
-  <si>
-    <t>TLLU7912887</t>
-  </si>
-  <si>
-    <t>CMAU8088116</t>
-  </si>
-  <si>
-    <t>CAAU6403722</t>
-  </si>
-  <si>
-    <t>FSCU8051575</t>
-  </si>
-  <si>
-    <t>MSBU5538326</t>
-  </si>
-  <si>
-    <t>OOCU9763508</t>
-  </si>
-  <si>
-    <t>TCKU7044660</t>
-  </si>
-  <si>
-    <t>MSBU7211158</t>
-  </si>
-  <si>
-    <t>MSMU5045410</t>
-  </si>
-  <si>
-    <t>TCLU7868359</t>
-  </si>
-  <si>
-    <t>CMAU2551687</t>
-  </si>
-  <si>
-    <t>ECMU2988725</t>
-  </si>
-  <si>
-    <t>FCIU4157410</t>
-  </si>
-  <si>
-    <t>ECMU8146513</t>
-  </si>
-  <si>
-    <t>FFAU5018140</t>
-  </si>
-  <si>
-    <t>MRKU3325317</t>
-  </si>
-  <si>
-    <t>SUDU6988807</t>
-  </si>
-  <si>
-    <t>MSBU6799258</t>
-  </si>
-  <si>
-    <t>FCIU9092857</t>
-  </si>
-  <si>
-    <t>TCLU6070528</t>
-  </si>
-  <si>
-    <t>TLLU1513581</t>
-  </si>
-  <si>
-    <t>CAAU5305151</t>
-  </si>
-  <si>
-    <t>DFSU3135195</t>
-  </si>
-  <si>
-    <t>HMMU4375392</t>
-  </si>
-  <si>
-    <t>TCNU2623495</t>
-  </si>
-  <si>
-    <t>CAIU8187836</t>
-  </si>
-  <si>
-    <t>CAIU8195019</t>
-  </si>
-  <si>
-    <t>CAXU9597210</t>
-  </si>
-  <si>
-    <t>CRSU9285030</t>
-  </si>
-  <si>
-    <t>CXDU1343113</t>
-  </si>
-  <si>
-    <t>FCGU1985650</t>
-  </si>
-  <si>
-    <t>GESU5754754</t>
-  </si>
-  <si>
-    <t>GESU6611779</t>
-  </si>
-  <si>
-    <t>HJMU1333462</t>
-  </si>
-  <si>
-    <t>HJMU1526899</t>
-  </si>
-  <si>
-    <t>SEGU4664326</t>
-  </si>
-  <si>
-    <t>TCNU6466917</t>
-  </si>
-  <si>
-    <t>TEXU8950776</t>
-  </si>
-  <si>
-    <t>TEXU8950777</t>
-  </si>
-  <si>
-    <t>TEXU8950778</t>
-  </si>
-  <si>
-    <t>TEXU8950779</t>
-  </si>
-  <si>
-    <t>TEXU8950780</t>
-  </si>
-  <si>
-    <t>TEXU8950781</t>
-  </si>
-  <si>
-    <t>TEXU8950782</t>
-  </si>
-  <si>
-    <t>TEXU8950783</t>
-  </si>
-  <si>
-    <t>TEXU8950784</t>
-  </si>
-  <si>
-    <t>TEXU8950785</t>
-  </si>
-  <si>
-    <t>TEXU8950786</t>
-  </si>
-  <si>
-    <t>MEDU7448653</t>
-  </si>
-  <si>
-    <t>MSKU1488791</t>
-  </si>
-  <si>
-    <t>MSKU1000227</t>
-  </si>
-  <si>
-    <t>CAIU9869825</t>
-  </si>
-  <si>
-    <t>MSDU6529537</t>
-  </si>
-  <si>
-    <t>MSNU5931330</t>
-  </si>
-  <si>
-    <t>MSDU8073810</t>
-  </si>
-  <si>
-    <t>MSNU5162977</t>
-  </si>
-  <si>
-    <t>DRY9392517</t>
-  </si>
-  <si>
-    <t>FDCU0098915</t>
-  </si>
-  <si>
-    <t>TRHU3068282</t>
-  </si>
-  <si>
-    <t>02 TCS</t>
-  </si>
-  <si>
-    <t>ARKU8406553</t>
-  </si>
-  <si>
-    <t>TRIU0582970</t>
-  </si>
-  <si>
-    <t>TGHU6294677</t>
-  </si>
-  <si>
-    <t>CMAU4616220</t>
-  </si>
-  <si>
-    <t>TRLU8256486</t>
-  </si>
-  <si>
-    <t>ARKU8428465</t>
-  </si>
-  <si>
-    <t>ARKU8480587</t>
-  </si>
-  <si>
-    <t>AXIU1625832</t>
-  </si>
-  <si>
-    <t>MRKU7902309</t>
-  </si>
-  <si>
-    <t>QIBU1243721</t>
-  </si>
-  <si>
-    <t>QNNU1237028</t>
-  </si>
-  <si>
-    <t>QIBU1242601</t>
-  </si>
-  <si>
-    <t>CLHU8240864</t>
-  </si>
-  <si>
-    <t>GSTU8852077</t>
-  </si>
-  <si>
-    <t>INKU2542677</t>
-  </si>
-  <si>
-    <t>CLHU8701668</t>
-  </si>
-  <si>
-    <t>HJCU1622629</t>
-  </si>
-  <si>
-    <t>MOTU0406709</t>
-  </si>
-  <si>
-    <t>CLMU5003937</t>
-  </si>
-  <si>
-    <t>HLXU6096790</t>
-  </si>
-  <si>
-    <t>SNFU5045866</t>
-  </si>
-  <si>
-    <t>GLDU0724429</t>
-  </si>
-  <si>
-    <t>HLXU6301235</t>
-  </si>
-  <si>
-    <t>TGHU7368326</t>
-  </si>
-  <si>
-    <t>MEDU6291077</t>
-  </si>
-  <si>
-    <t>TEMU5207486</t>
-  </si>
-  <si>
-    <t>GATU 865 7916</t>
-  </si>
-  <si>
-    <t>SCZU5716520</t>
-  </si>
-  <si>
-    <t>HJCU1110216</t>
-  </si>
-  <si>
-    <t>SKHU8307240</t>
-  </si>
-  <si>
-    <t>HLXU6295657</t>
-  </si>
-  <si>
-    <t>TCKU9135121</t>
-  </si>
-  <si>
-    <t>SCZU5716200</t>
-  </si>
-  <si>
-    <t>YMLU8220026</t>
-  </si>
-  <si>
-    <t>ECMU8066450</t>
-  </si>
-  <si>
-    <t>ECBU1405481</t>
-  </si>
-  <si>
-    <t>MOBU4532748</t>
-  </si>
-  <si>
-    <t>BEAU4673223</t>
-  </si>
-  <si>
-    <t>FFAU4537789</t>
-  </si>
-  <si>
-    <t>TGBU5352870</t>
-  </si>
-  <si>
-    <t>CMAU7086783</t>
-  </si>
-  <si>
-    <t>SEGU6053497</t>
-  </si>
-  <si>
-    <t>TLLU4268359</t>
-  </si>
-  <si>
-    <t>CMAU7262223</t>
-  </si>
-  <si>
-    <t>TCNU2631802</t>
-  </si>
-  <si>
-    <t>FFAU4472420</t>
-  </si>
-  <si>
-    <t>TCNU2937259</t>
-  </si>
-  <si>
-    <t>EMAU1013652</t>
-  </si>
-  <si>
-    <t>EMAU3029703</t>
-  </si>
-  <si>
-    <t>EMAU3017560</t>
-  </si>
-  <si>
-    <t>EMAU3039996</t>
-  </si>
-  <si>
-    <t>EMAU3018078</t>
-  </si>
-  <si>
-    <t>SGRU2014000</t>
-  </si>
-  <si>
-    <t>EMAU3025077</t>
-  </si>
-  <si>
-    <t>TRHU2574497</t>
-  </si>
-  <si>
-    <t>SEGU2796344</t>
-  </si>
-  <si>
-    <t>TCKU2370767</t>
-  </si>
-  <si>
     <t>202 15/07/2015</t>
   </si>
   <si>
@@ -712,13 +209,392 @@
   </si>
   <si>
     <t>COLIS</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>TC Réceptionnés</t>
+  </si>
+  <si>
+    <t>TC Sortis</t>
+  </si>
+  <si>
+    <t>Total Mouvements</t>
+  </si>
+  <si>
+    <t>TC Sortis
+VIDE</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>VH</t>
+  </si>
+  <si>
+    <t>ARKU840655 /3</t>
+  </si>
+  <si>
+    <t>TRIU058297 /0</t>
+  </si>
+  <si>
+    <t>TGHU629467 /7</t>
+  </si>
+  <si>
+    <t>CMAU461622 /0</t>
+  </si>
+  <si>
+    <t>TRLU825648 /6</t>
+  </si>
+  <si>
+    <t>ARKU842846 /5</t>
+  </si>
+  <si>
+    <t>ARKU848058 /7</t>
+  </si>
+  <si>
+    <t>AXIU162583 /2</t>
+  </si>
+  <si>
+    <t>MRKU790230 /9</t>
+  </si>
+  <si>
+    <t>QIBU124372 /1</t>
+  </si>
+  <si>
+    <t>QNNU123702 /8</t>
+  </si>
+  <si>
+    <t>QIBU124260 /1</t>
+  </si>
+  <si>
+    <t>CLHU824086 /4</t>
+  </si>
+  <si>
+    <t>GSTU885207 /7</t>
+  </si>
+  <si>
+    <t>INKU254267 /7</t>
+  </si>
+  <si>
+    <t>CLHU870166 /8</t>
+  </si>
+  <si>
+    <t>HJCU162262 /9</t>
+  </si>
+  <si>
+    <t>MOTU040670 /9</t>
+  </si>
+  <si>
+    <t>CLMU500393 /7</t>
+  </si>
+  <si>
+    <t>HLXU609679 /0</t>
+  </si>
+  <si>
+    <t>SNFU504586 /6</t>
+  </si>
+  <si>
+    <t>GLDU072442 /9</t>
+  </si>
+  <si>
+    <t>HLXU630123 /5</t>
+  </si>
+  <si>
+    <t>TGHU736832 /6</t>
+  </si>
+  <si>
+    <t>MEDU629107 /7</t>
+  </si>
+  <si>
+    <t>TEMU520748 /6</t>
+  </si>
+  <si>
+    <t>GATU865791 /6</t>
+  </si>
+  <si>
+    <t>SCZU571652 /0</t>
+  </si>
+  <si>
+    <t>HJCU111021 /6</t>
+  </si>
+  <si>
+    <t>SKHU830724 /0</t>
+  </si>
+  <si>
+    <t>HLXU629565 /7</t>
+  </si>
+  <si>
+    <t>TCKU913512 /1</t>
+  </si>
+  <si>
+    <t>SCZU571620 /0</t>
+  </si>
+  <si>
+    <t>YMLU822002 /6</t>
+  </si>
+  <si>
+    <t>ECMU806645 /0</t>
+  </si>
+  <si>
+    <t>ECBU140548 /1</t>
+  </si>
+  <si>
+    <t>MOBU453274 /8</t>
+  </si>
+  <si>
+    <t>BEAU467322 /3</t>
+  </si>
+  <si>
+    <t>FFAU453778 /9</t>
+  </si>
+  <si>
+    <t>TGBU535287 /0</t>
+  </si>
+  <si>
+    <t>CMAU708678 /3</t>
+  </si>
+  <si>
+    <t>SEGU605349 /7</t>
+  </si>
+  <si>
+    <t>TLLU426835 /9</t>
+  </si>
+  <si>
+    <t>CMAU726222 /3</t>
+  </si>
+  <si>
+    <t>TCNU263180 /2</t>
+  </si>
+  <si>
+    <t>FFAU447242 /0</t>
+  </si>
+  <si>
+    <t>TCNU293725 /9</t>
+  </si>
+  <si>
+    <t>EMAU101365 /2</t>
+  </si>
+  <si>
+    <t>EMAU302970 /3</t>
+  </si>
+  <si>
+    <t>EMAU301756 /0</t>
+  </si>
+  <si>
+    <t>EMAU303999 /6</t>
+  </si>
+  <si>
+    <t>EMAU301807 /8</t>
+  </si>
+  <si>
+    <t>SGRU201400 /0</t>
+  </si>
+  <si>
+    <t>EMAU302507 /7</t>
+  </si>
+  <si>
+    <t>TRHU257449 /7</t>
+  </si>
+  <si>
+    <t>SEGU279634 /4</t>
+  </si>
+  <si>
+    <t>TCKU237076 /7</t>
+  </si>
+  <si>
+    <t>MEDU703575 /8</t>
+  </si>
+  <si>
+    <t>MSMU601249 /5</t>
+  </si>
+  <si>
+    <t>MSMU662915 /2</t>
+  </si>
+  <si>
+    <t>AMCU800634 /8</t>
+  </si>
+  <si>
+    <t>AMCU801023 /0</t>
+  </si>
+  <si>
+    <t>TCLU481554 /5</t>
+  </si>
+  <si>
+    <t>TLLU167487 /9</t>
+  </si>
+  <si>
+    <t>FSCU873148 /5</t>
+  </si>
+  <si>
+    <t>TCNU338016 /8</t>
+  </si>
+  <si>
+    <t>CMAU789256 /2</t>
+  </si>
+  <si>
+    <t>MEDU623254 /1</t>
+  </si>
+  <si>
+    <t>MSCU536640 /5</t>
+  </si>
+  <si>
+    <t>MSCU546237 /4</t>
+  </si>
+  <si>
+    <t>MSDU859434 /1</t>
+  </si>
+  <si>
+    <t>TRHU508025 /0</t>
+  </si>
+  <si>
+    <t>TRHU873225 /0</t>
+  </si>
+  <si>
+    <t>CMAU965494 /3</t>
+  </si>
+  <si>
+    <t>HASU492916 /6</t>
+  </si>
+  <si>
+    <t>HASU5156746 /8</t>
+  </si>
+  <si>
+    <t>MRSU698006 /4</t>
+  </si>
+  <si>
+    <t>PONU804908 /6</t>
+  </si>
+  <si>
+    <t>TLLU805438 /1</t>
+  </si>
+  <si>
+    <t>APZU213305 /9</t>
+  </si>
+  <si>
+    <t>CMAU194208 /0</t>
+  </si>
+  <si>
+    <t>TEMU387154 /1</t>
+  </si>
+  <si>
+    <t>HASU512425 /3</t>
+  </si>
+  <si>
+    <t>MRKU714747 /1</t>
+  </si>
+  <si>
+    <t>MRKU776760 /0</t>
+  </si>
+  <si>
+    <t>MRKU862304 /2</t>
+  </si>
+  <si>
+    <t>MSKU561006 /4</t>
+  </si>
+  <si>
+    <t>SUDU747145 /0</t>
+  </si>
+  <si>
+    <t>TCKU302077 /9</t>
+  </si>
+  <si>
+    <t>TEMU342001 /8</t>
+  </si>
+  <si>
+    <t>HASU148037 /0</t>
+  </si>
+  <si>
+    <t>TCLU717677 /2</t>
+  </si>
+  <si>
+    <t>ARKU241132 /0</t>
+  </si>
+  <si>
+    <t>TRHU307416 /1</t>
+  </si>
+  <si>
+    <t>KOCU451131 /9</t>
+  </si>
+  <si>
+    <t>TLLU602255 /2</t>
+  </si>
+  <si>
+    <t>TLLU791288 /7</t>
+  </si>
+  <si>
+    <t>CMAU808811 /6</t>
+  </si>
+  <si>
+    <t>CAAU640372 /2</t>
+  </si>
+  <si>
+    <t>FSCU805157 /5</t>
+  </si>
+  <si>
+    <t>MSBU553832 /6</t>
+  </si>
+  <si>
+    <t>OOCU976350 /8</t>
+  </si>
+  <si>
+    <t>TCKU704466 /0</t>
+  </si>
+  <si>
+    <t>MSBU721115 /8</t>
+  </si>
+  <si>
+    <t>MSMU504541 /0</t>
+  </si>
+  <si>
+    <t>TCLU786835 /9</t>
+  </si>
+  <si>
+    <t>CMAU255168 /7</t>
+  </si>
+  <si>
+    <t>ECMU298872 /5</t>
+  </si>
+  <si>
+    <t>FCIU415741 /0</t>
+  </si>
+  <si>
+    <t>ECMU814651 /3</t>
+  </si>
+  <si>
+    <t>FFAU501814 /0</t>
+  </si>
+  <si>
+    <t>MRKU332531 /7</t>
+  </si>
+  <si>
+    <t>SUDU698880 /7</t>
+  </si>
+  <si>
+    <t>MSBU679925 /8</t>
+  </si>
+  <si>
+    <t>FCIU909285 /7</t>
+  </si>
+  <si>
+    <t>TCLU607052 /8</t>
+  </si>
+  <si>
+    <t>TLLU151358 /1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -775,8 +651,29 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF2C3E50"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -801,8 +698,32 @@
         <bgColor rgb="FF2C3E50"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B365D"/>
+        <bgColor rgb="FF1B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9F9"/>
+        <bgColor rgb="FFF8F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EAF8"/>
+        <bgColor rgb="FFD6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF3CF"/>
+        <bgColor rgb="FFFCF3CF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -906,11 +827,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDC3C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDC3C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDC3C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDC3C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -978,9 +914,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1007,6 +940,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1451,8 +1402,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73FB2CF0-73DA-47C1-B22C-892004AD8E84}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="35">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="36">
+        <f>'Douanes Oran-Exterieur'!H1</f>
+        <v>60</v>
+      </c>
+      <c r="C2" s="36">
+        <v>0</v>
+      </c>
+      <c r="D2" s="37">
+        <f t="shared" ref="D2:D6" si="0">SUM(B2:C2)</f>
+        <v>60</v>
+      </c>
+      <c r="F2" s="36"/>
+    </row>
+    <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="35">
+        <v>46267</v>
+      </c>
+      <c r="B3" s="36">
+        <f>'Douanes Oran-Port'!H1</f>
+        <v>59</v>
+      </c>
+      <c r="C3" s="36">
+        <v>0</v>
+      </c>
+      <c r="D3" s="37">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="F3" s="36"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="F4" s="36"/>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="37"/>
+      <c r="F5" s="36"/>
+    </row>
+    <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="35"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="37"/>
+      <c r="F6" s="36"/>
+    </row>
+    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="35"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="37"/>
+      <c r="F7" s="36"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="35"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="37"/>
+      <c r="F8" s="36"/>
+    </row>
+    <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="35"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="37"/>
+      <c r="F9" s="36"/>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="37"/>
+      <c r="F10" s="36"/>
+    </row>
+    <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="37"/>
+      <c r="F11" s="36"/>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="37"/>
+      <c r="F12" s="36"/>
+    </row>
+    <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37"/>
+      <c r="F13" s="36"/>
+    </row>
+    <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
+      <c r="F14" s="36"/>
+    </row>
+    <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="35"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="37"/>
+      <c r="F15" s="36"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="35"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="F16" s="36"/>
+    </row>
+    <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="35"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="F17" s="36"/>
+    </row>
+    <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="35"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
+      <c r="F18" s="36"/>
+    </row>
+    <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="F19" s="36"/>
+    </row>
+    <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="F20" s="36"/>
+    </row>
+    <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="35"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="F21" s="36"/>
+    </row>
+    <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="35"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="37"/>
+      <c r="F22" s="36"/>
+    </row>
+    <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="F23" s="36"/>
+    </row>
+    <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="38">
+        <f>SUM(B2:B22)</f>
+        <v>119</v>
+      </c>
+      <c r="C24" s="38">
+        <f>SUM(C2:C22)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="38">
+        <f>SUM(D2:D22)</f>
+        <v>119</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3487DF-D1A0-4D00-8014-E47488D932D5}">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="16" bestFit="1" customWidth="1"/>
@@ -1470,29 +1646,46 @@
     <row r="1" spans="1:10" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
+      <c r="H1" s="3">
+        <f>COUNTIF(C8:C67,"&lt;&gt;")</f>
+        <v>60</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="F2" s="3">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="39">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="5">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1537,14 +1730,14 @@
       <c r="A8" s="12">
         <v>1</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="31" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="21">
         <v>45526</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="14">
@@ -1556,10 +1749,12 @@
       <c r="A9" s="12">
         <v>2</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="22"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="21">
+        <v>45526</v>
+      </c>
       <c r="D9" s="22" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
@@ -1569,10 +1764,12 @@
       <c r="A10" s="12">
         <v>3</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="22"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="21">
+        <v>45526</v>
+      </c>
       <c r="D10" s="22" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
@@ -1582,14 +1779,14 @@
       <c r="A11" s="12">
         <v>4</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="31" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="21">
         <v>45537</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
@@ -1599,10 +1796,12 @@
       <c r="A12" s="12">
         <v>5</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="22"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="21">
+        <v>45537</v>
+      </c>
       <c r="D12" s="22" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="14"/>
@@ -1612,10 +1811,12 @@
       <c r="A13" s="12">
         <v>6</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="22"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="21">
+        <v>45537</v>
+      </c>
       <c r="D13" s="22" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="E13" s="17"/>
       <c r="F13" s="14"/>
@@ -1625,10 +1826,12 @@
       <c r="A14" s="12">
         <v>7</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="22"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="21">
+        <v>45537</v>
+      </c>
       <c r="D14" s="22" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E14" s="17"/>
       <c r="F14" s="14"/>
@@ -1645,7 +1848,7 @@
         <v>45684</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E15" s="17"/>
       <c r="F15" s="14"/>
@@ -1662,7 +1865,7 @@
         <v>45724</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="20"/>
@@ -1678,7 +1881,7 @@
         <v>45729</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="E17" s="20"/>
       <c r="F17" s="20"/>
@@ -1687,14 +1890,14 @@
       <c r="A18" s="12">
         <v>11</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="31" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="21">
         <v>45817</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="E18" s="20"/>
       <c r="F18" s="20"/>
@@ -1703,10 +1906,12 @@
       <c r="A19" s="12">
         <v>12</v>
       </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="22"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="21">
+        <v>45817</v>
+      </c>
       <c r="D19" s="22" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="E19" s="20"/>
       <c r="F19" s="20"/>
@@ -1715,10 +1920,12 @@
       <c r="A20" s="12">
         <v>13</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="22"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="21">
+        <v>45817</v>
+      </c>
       <c r="D20" s="22" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="E20" s="20"/>
       <c r="F20" s="20"/>
@@ -1727,10 +1934,12 @@
       <c r="A21" s="12">
         <v>14</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="22"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="21">
+        <v>45817</v>
+      </c>
       <c r="D21" s="22" t="s">
-        <v>61</v>
+        <v>134</v>
       </c>
       <c r="E21" s="20"/>
       <c r="F21" s="20"/>
@@ -1739,10 +1948,12 @@
       <c r="A22" s="12">
         <v>15</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="22"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="21">
+        <v>45817</v>
+      </c>
       <c r="D22" s="22" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="E22" s="20"/>
       <c r="F22" s="20"/>
@@ -1751,10 +1962,12 @@
       <c r="A23" s="12">
         <v>16</v>
       </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="22"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="21">
+        <v>45817</v>
+      </c>
       <c r="D23" s="22" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="E23" s="20"/>
       <c r="F23" s="20"/>
@@ -1770,7 +1983,7 @@
         <v>46189</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="E24" s="20"/>
       <c r="F24" s="20"/>
@@ -1779,14 +1992,14 @@
       <c r="A25" s="12">
         <v>18</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="31" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="21">
         <v>45862</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E25" s="20"/>
       <c r="F25" s="20"/>
@@ -1795,10 +2008,12 @@
       <c r="A26" s="12">
         <v>19</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="22"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="21">
+        <v>45862</v>
+      </c>
       <c r="D26" s="22" t="s">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
@@ -1807,10 +2022,12 @@
       <c r="A27" s="12">
         <v>20</v>
       </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="22"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="21">
+        <v>45862</v>
+      </c>
       <c r="D27" s="22" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="E27" s="20"/>
       <c r="F27" s="20"/>
@@ -1819,14 +2036,14 @@
       <c r="A28" s="12">
         <v>21</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="21">
         <v>45867</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="E28" s="20"/>
       <c r="F28" s="20"/>
@@ -1835,10 +2052,12 @@
       <c r="A29" s="12">
         <v>22</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="22"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="21">
+        <v>45867</v>
+      </c>
       <c r="D29" s="22" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="E29" s="20"/>
       <c r="F29" s="20"/>
@@ -1847,14 +2066,14 @@
       <c r="A30" s="12">
         <v>23</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="31" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="21">
         <v>45869</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="E30" s="20"/>
       <c r="F30" s="20"/>
@@ -1863,10 +2082,12 @@
       <c r="A31" s="12">
         <v>24</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="22"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="21">
+        <v>45869</v>
+      </c>
       <c r="D31" s="22" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="E31" s="20"/>
       <c r="F31" s="20"/>
@@ -1875,10 +2096,12 @@
       <c r="A32" s="12">
         <v>25</v>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="22"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="21">
+        <v>45869</v>
+      </c>
       <c r="D32" s="22" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="E32" s="20"/>
       <c r="F32" s="20"/>
@@ -1894,7 +2117,7 @@
         <v>45880</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="E33" s="20"/>
       <c r="F33" s="20"/>
@@ -1903,14 +2126,14 @@
       <c r="A34" s="12">
         <v>27</v>
       </c>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="31" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="21">
         <v>45889</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="E34" s="20"/>
       <c r="F34" s="20"/>
@@ -1919,10 +2142,12 @@
       <c r="A35" s="12">
         <v>28</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="22"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="21">
+        <v>45889</v>
+      </c>
       <c r="D35" s="22" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="E35" s="20"/>
       <c r="F35" s="20"/>
@@ -1931,10 +2156,12 @@
       <c r="A36" s="12">
         <v>29</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="22"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="21">
+        <v>45889</v>
+      </c>
       <c r="D36" s="22" t="s">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="E36" s="20"/>
       <c r="F36" s="20"/>
@@ -1943,10 +2170,12 @@
       <c r="A37" s="12">
         <v>30</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="22"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="21">
+        <v>45889</v>
+      </c>
       <c r="D37" s="22" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="E37" s="20"/>
       <c r="F37" s="20"/>
@@ -1955,10 +2184,12 @@
       <c r="A38" s="12">
         <v>31</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="22"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="21">
+        <v>45889</v>
+      </c>
       <c r="D38" s="22" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="E38" s="20"/>
       <c r="F38" s="20"/>
@@ -1967,10 +2198,12 @@
       <c r="A39" s="12">
         <v>32</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="22"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="21">
+        <v>45889</v>
+      </c>
       <c r="D39" s="22" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E39" s="20"/>
       <c r="F39" s="20"/>
@@ -1979,10 +2212,12 @@
       <c r="A40" s="12">
         <v>33</v>
       </c>
-      <c r="B40" s="33"/>
-      <c r="C40" s="22"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="21">
+        <v>45889</v>
+      </c>
       <c r="D40" s="22" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="E40" s="20"/>
       <c r="F40" s="20"/>
@@ -1991,14 +2226,14 @@
       <c r="A41" s="12">
         <v>34</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="31" t="s">
         <v>20</v>
       </c>
       <c r="C41" s="21">
         <v>45895</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E41" s="20"/>
       <c r="F41" s="20"/>
@@ -2007,10 +2242,12 @@
       <c r="A42" s="12">
         <v>35</v>
       </c>
-      <c r="B42" s="33"/>
-      <c r="C42" s="22"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="21">
+        <v>45895</v>
+      </c>
       <c r="D42" s="22" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="E42" s="20"/>
       <c r="F42" s="20"/>
@@ -2019,14 +2256,14 @@
       <c r="A43" s="12">
         <v>36</v>
       </c>
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="31" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="21">
         <v>46290</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="E43" s="20"/>
       <c r="F43" s="20"/>
@@ -2035,10 +2272,12 @@
       <c r="A44" s="12">
         <v>37</v>
       </c>
-      <c r="B44" s="33"/>
-      <c r="C44" s="22"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="21">
+        <v>46290</v>
+      </c>
       <c r="D44" s="22" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="E44" s="20"/>
       <c r="F44" s="20"/>
@@ -2047,14 +2286,14 @@
       <c r="A45" s="12">
         <v>38</v>
       </c>
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="22" t="s">
-        <v>146</v>
+      <c r="C45" s="21">
+        <v>46032</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="E45" s="20"/>
       <c r="F45" s="20"/>
@@ -2063,10 +2302,12 @@
       <c r="A46" s="12">
         <v>39</v>
       </c>
-      <c r="B46" s="33"/>
-      <c r="C46" s="22"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="21">
+        <v>46032</v>
+      </c>
       <c r="D46" s="22" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="E46" s="20"/>
       <c r="F46" s="20"/>
@@ -2082,7 +2323,7 @@
         <v>46034</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="E47" s="20"/>
       <c r="F47" s="20"/>
@@ -2098,7 +2339,7 @@
         <v>45672</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>88</v>
+        <v>161</v>
       </c>
       <c r="E48" s="20"/>
       <c r="F48" s="20"/>
@@ -2114,7 +2355,7 @@
         <v>46078</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="E49" s="20"/>
       <c r="F49" s="20"/>
@@ -2130,7 +2371,7 @@
         <v>46119</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="E50" s="20"/>
       <c r="F50" s="20"/>
@@ -2146,7 +2387,7 @@
         <v>46125</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="E51" s="20"/>
       <c r="F51" s="20"/>
@@ -2155,14 +2396,14 @@
       <c r="A52" s="12">
         <v>45</v>
       </c>
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="31" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="21">
         <v>46125</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="E52" s="20"/>
       <c r="F52" s="20"/>
@@ -2171,10 +2412,12 @@
       <c r="A53" s="12">
         <v>46</v>
       </c>
-      <c r="B53" s="33"/>
-      <c r="C53" s="22"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="21">
+        <v>46125</v>
+      </c>
       <c r="D53" s="22" t="s">
-        <v>93</v>
+        <v>166</v>
       </c>
       <c r="E53" s="20"/>
       <c r="F53" s="20"/>
@@ -2183,14 +2426,14 @@
       <c r="A54" s="12">
         <v>47</v>
       </c>
-      <c r="B54" s="32" t="s">
+      <c r="B54" s="31" t="s">
         <v>29</v>
       </c>
       <c r="C54" s="21">
         <v>46134</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="E54" s="20"/>
       <c r="F54" s="20"/>
@@ -2199,10 +2442,12 @@
       <c r="A55" s="12">
         <v>48</v>
       </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="22"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="21">
+        <v>46134</v>
+      </c>
       <c r="D55" s="22" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="E55" s="20"/>
       <c r="F55" s="20"/>
@@ -2211,10 +2456,12 @@
       <c r="A56" s="12">
         <v>49</v>
       </c>
-      <c r="B56" s="33"/>
-      <c r="C56" s="22"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="21">
+        <v>46134</v>
+      </c>
       <c r="D56" s="22" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="E56" s="20"/>
       <c r="F56" s="20"/>
@@ -2223,14 +2470,14 @@
       <c r="A57" s="12">
         <v>50</v>
       </c>
-      <c r="B57" s="32" t="s">
+      <c r="B57" s="31" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="21">
         <v>46135</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="E57" s="20"/>
       <c r="F57" s="20"/>
@@ -2239,10 +2486,12 @@
       <c r="A58" s="12">
         <v>51</v>
       </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="22"/>
+      <c r="B58" s="33"/>
+      <c r="C58" s="21">
+        <v>46135</v>
+      </c>
       <c r="D58" s="22" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="E58" s="20"/>
       <c r="F58" s="20"/>
@@ -2251,10 +2500,12 @@
       <c r="A59" s="12">
         <v>52</v>
       </c>
-      <c r="B59" s="33"/>
-      <c r="C59" s="22"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="21">
+        <v>46135</v>
+      </c>
       <c r="D59" s="22" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="E59" s="20"/>
       <c r="F59" s="20"/>
@@ -2270,7 +2521,7 @@
         <v>46138</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="E60" s="20"/>
       <c r="F60" s="20"/>
@@ -2286,7 +2537,7 @@
         <v>46138</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="E61" s="20"/>
       <c r="F61" s="20"/>
@@ -2295,14 +2546,14 @@
       <c r="A62" s="12">
         <v>55</v>
       </c>
-      <c r="B62" s="32" t="s">
+      <c r="B62" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C62" s="21">
         <v>46163</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="E62" s="20"/>
       <c r="F62" s="20"/>
@@ -2311,10 +2562,12 @@
       <c r="A63" s="12">
         <v>56</v>
       </c>
-      <c r="B63" s="33"/>
-      <c r="C63" s="22"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="21">
+        <v>46163</v>
+      </c>
       <c r="D63" s="22" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="E63" s="20"/>
       <c r="F63" s="20"/>
@@ -2330,7 +2583,7 @@
         <v>46149</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="E64" s="20"/>
       <c r="F64" s="20"/>
@@ -2339,14 +2592,14 @@
       <c r="A65" s="12">
         <v>58</v>
       </c>
-      <c r="B65" s="32" t="s">
+      <c r="B65" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C65" s="21">
         <v>46156</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="E65" s="20"/>
       <c r="F65" s="20"/>
@@ -2355,10 +2608,12 @@
       <c r="A66" s="12">
         <v>59</v>
       </c>
-      <c r="B66" s="34"/>
-      <c r="C66" s="22"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="21">
+        <v>46156</v>
+      </c>
       <c r="D66" s="22" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="E66" s="20"/>
       <c r="F66" s="20"/>
@@ -2367,520 +2622,22 @@
       <c r="A67" s="12">
         <v>60</v>
       </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="22"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="21">
+        <v>46156</v>
+      </c>
       <c r="D67" s="22" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="E67" s="20"/>
       <c r="F67" s="20"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="12">
-        <v>61</v>
-      </c>
-      <c r="B68" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C68" s="21">
-        <v>46162</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="12">
-        <v>62</v>
-      </c>
-      <c r="B69" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C69" s="21">
-        <v>46162</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="12">
-        <v>63</v>
-      </c>
-      <c r="B70" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C70" s="21">
-        <v>46176</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="12">
-        <v>64</v>
-      </c>
-      <c r="B71" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C71" s="21">
-        <v>46176</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="12">
-        <v>65</v>
-      </c>
-      <c r="B72" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C72" s="21">
-        <v>46183</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="12">
-        <v>66</v>
-      </c>
-      <c r="B73" s="34"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="12">
-        <v>67</v>
-      </c>
-      <c r="B74" s="34"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="12">
-        <v>68</v>
-      </c>
-      <c r="B75" s="34"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="12">
-        <v>69</v>
-      </c>
-      <c r="B76" s="34"/>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="12">
-        <v>70</v>
-      </c>
-      <c r="B77" s="34"/>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="12">
-        <v>71</v>
-      </c>
-      <c r="B78" s="34"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="12">
-        <v>72</v>
-      </c>
-      <c r="B79" s="34"/>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="12">
-        <v>73</v>
-      </c>
-      <c r="B80" s="34"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="12">
-        <v>74</v>
-      </c>
-      <c r="B81" s="34"/>
-      <c r="C81" s="22"/>
-      <c r="D81" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="12">
-        <v>75</v>
-      </c>
-      <c r="B82" s="34"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="12">
-        <v>76</v>
-      </c>
-      <c r="B83" s="34"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="12">
-        <v>77</v>
-      </c>
-      <c r="B84" s="34"/>
-      <c r="C84" s="22"/>
-      <c r="D84" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="12">
-        <v>78</v>
-      </c>
-      <c r="B85" s="34"/>
-      <c r="C85" s="22"/>
-      <c r="D85" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E85" s="20"/>
-      <c r="F85" s="20"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="12">
-        <v>79</v>
-      </c>
-      <c r="B86" s="34"/>
-      <c r="C86" s="22"/>
-      <c r="D86" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="12">
-        <v>80</v>
-      </c>
-      <c r="B87" s="34"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="12">
-        <v>81</v>
-      </c>
-      <c r="B88" s="34"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="12">
-        <v>82</v>
-      </c>
-      <c r="B89" s="34"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="12">
-        <v>83</v>
-      </c>
-      <c r="B90" s="34"/>
-      <c r="C90" s="22"/>
-      <c r="D90" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E90" s="20"/>
-      <c r="F90" s="20"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="12">
-        <v>84</v>
-      </c>
-      <c r="B91" s="34"/>
-      <c r="C91" s="22"/>
-      <c r="D91" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E91" s="20"/>
-      <c r="F91" s="20"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="12">
-        <v>85</v>
-      </c>
-      <c r="B92" s="34"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="12">
-        <v>86</v>
-      </c>
-      <c r="B93" s="34"/>
-      <c r="C93" s="22"/>
-      <c r="D93" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="E93" s="20"/>
-      <c r="F93" s="20"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="12">
-        <v>87</v>
-      </c>
-      <c r="B94" s="33"/>
-      <c r="C94" s="22"/>
-      <c r="D94" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E94" s="20"/>
-      <c r="F94" s="20"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="12">
-        <v>88</v>
-      </c>
-      <c r="B95" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C95" s="21">
-        <v>46194</v>
-      </c>
-      <c r="D95" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E95" s="20"/>
-      <c r="F95" s="20"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="12">
-        <v>89</v>
-      </c>
-      <c r="B96" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C96" s="21">
-        <v>46176</v>
-      </c>
-      <c r="D96" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E96" s="20"/>
-      <c r="F96" s="20"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="12">
-        <v>90</v>
-      </c>
-      <c r="B97" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C97" s="21">
-        <v>46176</v>
-      </c>
-      <c r="D97" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E97" s="20"/>
-      <c r="F97" s="20"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="12">
-        <v>91</v>
-      </c>
-      <c r="B98" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="C98" s="21">
-        <v>46176</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E98" s="20"/>
-      <c r="F98" s="20"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="12">
-        <v>92</v>
-      </c>
-      <c r="B99" s="34"/>
-      <c r="C99" s="22"/>
-      <c r="D99" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="E99" s="20"/>
-      <c r="F99" s="20"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="12">
-        <v>93</v>
-      </c>
-      <c r="B100" s="33"/>
-      <c r="C100" s="22"/>
-      <c r="D100" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="12">
-        <v>94</v>
-      </c>
-      <c r="B101" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C101" s="21">
-        <v>46180</v>
-      </c>
-      <c r="D101" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="E101" s="20"/>
-      <c r="F101" s="20"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="12">
-        <v>95</v>
-      </c>
-      <c r="B102" s="33"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E102" s="20"/>
-      <c r="F102" s="20"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="12">
-        <v>96</v>
-      </c>
-      <c r="B103" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C103" s="21">
-        <v>46201</v>
-      </c>
-      <c r="D103" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E103" s="20"/>
-      <c r="F103" s="20"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="12">
-        <v>97</v>
-      </c>
-      <c r="B104" s="33"/>
-      <c r="C104" s="22"/>
-      <c r="D104" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E104" s="20"/>
-      <c r="F104" s="20"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="12">
-        <v>98</v>
-      </c>
-      <c r="B105" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C105" s="21">
-        <v>46202</v>
-      </c>
-      <c r="D105" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="E105" s="20"/>
-      <c r="F105" s="20"/>
-    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="16">
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B65:B67"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="B8:B10"/>
@@ -2893,14 +2650,6 @@
     <mergeCell ref="B41:B42"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="B72:B94"/>
-    <mergeCell ref="B98:B100"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15" xr:uid="{12DFF3D6-54A0-4528-9EAC-5174C4651E3E}">
@@ -2913,7 +2662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1251E3F9-698E-43CA-8FE3-4DE9FEA08D25}">
   <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2924,8 +2673,8 @@
     <col min="4" max="4" width="19.140625" style="19" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" style="16" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="11.42578125" style="16"/>
+    <col min="7" max="8" width="12.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.42578125" style="16"/>
     <col min="11" max="11" width="14.7109375" style="16" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="11.42578125" style="16"/>
   </cols>
@@ -2933,29 +2682,46 @@
     <row r="1" spans="1:10" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
+      <c r="H1" s="3">
+        <f>COUNTIF(C8:C66,"&lt;&gt;")</f>
+        <v>59</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="F2" s="3">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="39">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="5">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3000,14 +2766,14 @@
       <c r="A8" s="12">
         <v>1</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>219</v>
+      <c r="B8" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="C8" s="24">
         <v>42873</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>223</v>
+        <v>55</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="14"/>
@@ -3017,14 +2783,14 @@
       <c r="A9" s="12">
         <v>2</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>220</v>
+      <c r="B9" s="25" t="s">
+        <v>52</v>
       </c>
       <c r="C9" s="24">
         <v>44032</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>223</v>
+        <v>55</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="14"/>
@@ -3034,14 +2800,14 @@
       <c r="A10" s="12">
         <v>3</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>221</v>
+      <c r="B10" s="25" t="s">
+        <v>53</v>
       </c>
       <c r="C10" s="24">
         <v>43319</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10" s="14"/>
@@ -3051,14 +2817,14 @@
       <c r="A11" s="12">
         <v>4</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>222</v>
+      <c r="B11" s="25" t="s">
+        <v>54</v>
       </c>
       <c r="C11" s="24">
         <v>43605</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="14"/>
@@ -3068,14 +2834,14 @@
       <c r="A12" s="12">
         <v>5</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>204</v>
+      <c r="B12" s="26" t="s">
+        <v>36</v>
       </c>
       <c r="C12" s="24">
         <v>43611</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12" s="14"/>
@@ -3085,10 +2851,12 @@
       <c r="A13" s="12">
         <v>6</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="22"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="24">
+        <v>43611</v>
+      </c>
       <c r="D13" s="23" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="14"/>
@@ -3098,10 +2866,12 @@
       <c r="A14" s="12">
         <v>7</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="22"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="24">
+        <v>43611</v>
+      </c>
       <c r="D14" s="23" t="s">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="14"/>
@@ -3111,14 +2881,14 @@
       <c r="A15" s="12">
         <v>8</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>205</v>
+      <c r="B15" s="25" t="s">
+        <v>37</v>
       </c>
       <c r="C15" s="21">
         <v>45684</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="14"/>
@@ -3128,14 +2898,14 @@
       <c r="A16" s="12">
         <v>9</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>206</v>
+      <c r="B16" s="26" t="s">
+        <v>38</v>
       </c>
       <c r="C16" s="21">
         <v>45724</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="20"/>
@@ -3144,12 +2914,12 @@
       <c r="A17" s="12">
         <v>10</v>
       </c>
-      <c r="B17" s="29"/>
+      <c r="B17" s="28"/>
       <c r="C17" s="21">
         <v>45729</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="E17" s="18"/>
       <c r="F17" s="20"/>
@@ -3158,14 +2928,14 @@
       <c r="A18" s="12">
         <v>11</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>207</v>
+      <c r="B18" s="25" t="s">
+        <v>39</v>
       </c>
       <c r="C18" s="21">
         <v>45817</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="20"/>
@@ -3174,12 +2944,14 @@
       <c r="A19" s="12">
         <v>12</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" s="22"/>
+      <c r="B19" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="21">
+        <v>45817</v>
+      </c>
       <c r="D19" s="23" t="s">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="20"/>
@@ -3188,10 +2960,12 @@
       <c r="A20" s="12">
         <v>13</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="22"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="21">
+        <v>45817</v>
+      </c>
       <c r="D20" s="23" t="s">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="20"/>
@@ -3200,10 +2974,12 @@
       <c r="A21" s="12">
         <v>14</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="22"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="21">
+        <v>45817</v>
+      </c>
       <c r="D21" s="23" t="s">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="20"/>
@@ -3212,12 +2988,14 @@
       <c r="A22" s="12">
         <v>15</v>
       </c>
-      <c r="B22" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="C22" s="22"/>
+      <c r="B22" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="21">
+        <v>46189</v>
+      </c>
       <c r="D22" s="23" t="s">
-        <v>159</v>
+        <v>76</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="20"/>
@@ -3226,10 +3004,12 @@
       <c r="A23" s="12">
         <v>16</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="22"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="21">
+        <v>46189</v>
+      </c>
       <c r="D23" s="23" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="20"/>
@@ -3238,12 +3018,12 @@
       <c r="A24" s="12">
         <v>17</v>
       </c>
-      <c r="B24" s="28"/>
+      <c r="B24" s="27"/>
       <c r="C24" s="21">
         <v>46189</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="20"/>
@@ -3252,12 +3032,12 @@
       <c r="A25" s="12">
         <v>18</v>
       </c>
-      <c r="B25" s="28"/>
+      <c r="B25" s="27"/>
       <c r="C25" s="21">
         <v>45862</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="20"/>
@@ -3266,10 +3046,12 @@
       <c r="A26" s="12">
         <v>19</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="22"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="21">
+        <v>45862</v>
+      </c>
       <c r="D26" s="23" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="20"/>
@@ -3278,10 +3060,12 @@
       <c r="A27" s="12">
         <v>20</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="22"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="21">
+        <v>45862</v>
+      </c>
       <c r="D27" s="23" t="s">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="20"/>
@@ -3290,12 +3074,12 @@
       <c r="A28" s="12">
         <v>21</v>
       </c>
-      <c r="B28" s="28"/>
+      <c r="B28" s="27"/>
       <c r="C28" s="21">
         <v>45867</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="20"/>
@@ -3304,10 +3088,12 @@
       <c r="A29" s="12">
         <v>22</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="22"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="21">
+        <v>45867</v>
+      </c>
       <c r="D29" s="23" t="s">
-        <v>166</v>
+        <v>83</v>
       </c>
       <c r="E29" s="18"/>
       <c r="F29" s="20"/>
@@ -3316,12 +3102,12 @@
       <c r="A30" s="12">
         <v>23</v>
       </c>
-      <c r="B30" s="28"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="21">
         <v>45869</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="E30" s="18"/>
       <c r="F30" s="20"/>
@@ -3330,10 +3116,12 @@
       <c r="A31" s="12">
         <v>24</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="22"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="21">
+        <v>45869</v>
+      </c>
       <c r="D31" s="23" t="s">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="E31" s="18"/>
       <c r="F31" s="20"/>
@@ -3342,10 +3130,12 @@
       <c r="A32" s="12">
         <v>25</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="22"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="21">
+        <v>45869</v>
+      </c>
       <c r="D32" s="23" t="s">
-        <v>169</v>
+        <v>86</v>
       </c>
       <c r="E32" s="18"/>
       <c r="F32" s="20"/>
@@ -3354,12 +3144,12 @@
       <c r="A33" s="12">
         <v>26</v>
       </c>
-      <c r="B33" s="29"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="21">
-        <v>45880</v>
+        <v>45869</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="E33" s="18"/>
       <c r="F33" s="20"/>
@@ -3368,14 +3158,14 @@
       <c r="A34" s="12">
         <v>27</v>
       </c>
-      <c r="B34" s="26" t="s">
-        <v>210</v>
+      <c r="B34" s="25" t="s">
+        <v>42</v>
       </c>
       <c r="C34" s="21">
         <v>45889</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>171</v>
+        <v>88</v>
       </c>
       <c r="E34" s="18"/>
       <c r="F34" s="20"/>
@@ -3384,12 +3174,14 @@
       <c r="A35" s="12">
         <v>28</v>
       </c>
-      <c r="B35" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="C35" s="22"/>
+      <c r="B35" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="21">
+        <v>45889</v>
+      </c>
       <c r="D35" s="23" t="s">
-        <v>172</v>
+        <v>89</v>
       </c>
       <c r="E35" s="18"/>
       <c r="F35" s="20"/>
@@ -3398,12 +3190,14 @@
       <c r="A36" s="12">
         <v>29</v>
       </c>
-      <c r="B36" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="C36" s="22"/>
+      <c r="B36" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="21">
+        <v>45889</v>
+      </c>
       <c r="D36" s="23" t="s">
-        <v>173</v>
+        <v>90</v>
       </c>
       <c r="E36" s="18"/>
       <c r="F36" s="20"/>
@@ -3412,10 +3206,12 @@
       <c r="A37" s="12">
         <v>30</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="22"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="21">
+        <v>45889</v>
+      </c>
       <c r="D37" s="23" t="s">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="E37" s="18"/>
       <c r="F37" s="20"/>
@@ -3424,10 +3220,12 @@
       <c r="A38" s="12">
         <v>31</v>
       </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="22"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="21">
+        <v>45889</v>
+      </c>
       <c r="D38" s="23" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="E38" s="18"/>
       <c r="F38" s="20"/>
@@ -3436,10 +3234,12 @@
       <c r="A39" s="12">
         <v>32</v>
       </c>
-      <c r="B39" s="28"/>
-      <c r="C39" s="22"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="21">
+        <v>45889</v>
+      </c>
       <c r="D39" s="23" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39" s="20"/>
@@ -3448,10 +3248,12 @@
       <c r="A40" s="12">
         <v>33</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="22"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="21">
+        <v>45889</v>
+      </c>
       <c r="D40" s="23" t="s">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="E40" s="18"/>
       <c r="F40" s="20"/>
@@ -3460,12 +3262,12 @@
       <c r="A41" s="12">
         <v>34</v>
       </c>
-      <c r="B41" s="28"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="21">
         <v>45895</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="E41" s="18"/>
       <c r="F41" s="20"/>
@@ -3474,10 +3276,12 @@
       <c r="A42" s="12">
         <v>35</v>
       </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="22"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="21">
+        <v>45895</v>
+      </c>
       <c r="D42" s="23" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42" s="20"/>
@@ -3486,12 +3290,12 @@
       <c r="A43" s="12">
         <v>36</v>
       </c>
-      <c r="B43" s="29"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="21">
         <v>46290</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43" s="20"/>
@@ -3500,12 +3304,14 @@
       <c r="A44" s="12">
         <v>37</v>
       </c>
-      <c r="B44" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="C44" s="22"/>
+      <c r="B44" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="21">
+        <v>46290</v>
+      </c>
       <c r="D44" s="23" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="E44" s="18"/>
       <c r="F44" s="20"/>
@@ -3514,14 +3320,14 @@
       <c r="A45" s="12">
         <v>38</v>
       </c>
-      <c r="B45" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>146</v>
+      <c r="B45" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="21">
+        <v>46290</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="E45" s="18"/>
       <c r="F45" s="20"/>
@@ -3530,12 +3336,14 @@
       <c r="A46" s="12">
         <v>39</v>
       </c>
-      <c r="B46" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="C46" s="22"/>
+      <c r="B46" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="21">
+        <v>46290</v>
+      </c>
       <c r="D46" s="23" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="E46" s="18"/>
       <c r="F46" s="20"/>
@@ -3544,14 +3352,14 @@
       <c r="A47" s="12">
         <v>40</v>
       </c>
-      <c r="B47" s="27" t="s">
-        <v>216</v>
+      <c r="B47" s="26" t="s">
+        <v>48</v>
       </c>
       <c r="C47" s="21">
         <v>46034</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="E47" s="18"/>
       <c r="F47" s="20"/>
@@ -3560,12 +3368,12 @@
       <c r="A48" s="12">
         <v>41</v>
       </c>
-      <c r="B48" s="28"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="21">
         <v>45672</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="E48" s="18"/>
       <c r="F48" s="20"/>
@@ -3574,12 +3382,12 @@
       <c r="A49" s="12">
         <v>42</v>
       </c>
-      <c r="B49" s="28"/>
+      <c r="B49" s="27"/>
       <c r="C49" s="21">
         <v>46078</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="20"/>
@@ -3588,12 +3396,12 @@
       <c r="A50" s="12">
         <v>43</v>
       </c>
-      <c r="B50" s="28"/>
+      <c r="B50" s="27"/>
       <c r="C50" s="21">
         <v>46119</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="E50" s="18"/>
       <c r="F50" s="20"/>
@@ -3602,12 +3410,12 @@
       <c r="A51" s="12">
         <v>44</v>
       </c>
-      <c r="B51" s="28"/>
+      <c r="B51" s="27"/>
       <c r="C51" s="21">
         <v>46125</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="E51" s="18"/>
       <c r="F51" s="20"/>
@@ -3616,12 +3424,12 @@
       <c r="A52" s="12">
         <v>45</v>
       </c>
-      <c r="B52" s="28"/>
+      <c r="B52" s="27"/>
       <c r="C52" s="21">
         <v>46125</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="E52" s="18"/>
       <c r="F52" s="20"/>
@@ -3630,10 +3438,12 @@
       <c r="A53" s="12">
         <v>46</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="22"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="21">
+        <v>46125</v>
+      </c>
       <c r="D53" s="23" t="s">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="E53" s="18"/>
       <c r="F53" s="20"/>
@@ -3642,12 +3452,12 @@
       <c r="A54" s="12">
         <v>47</v>
       </c>
-      <c r="B54" s="28"/>
+      <c r="B54" s="27"/>
       <c r="C54" s="21">
         <v>46134</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>191</v>
+        <v>108</v>
       </c>
       <c r="E54" s="18"/>
       <c r="F54" s="20"/>
@@ -3656,10 +3466,12 @@
       <c r="A55" s="12">
         <v>48</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="22"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="21">
+        <v>46134</v>
+      </c>
       <c r="D55" s="23" t="s">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="E55" s="18"/>
       <c r="F55" s="20"/>
@@ -3668,10 +3480,12 @@
       <c r="A56" s="12">
         <v>49</v>
       </c>
-      <c r="B56" s="29"/>
-      <c r="C56" s="22"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="21">
+        <v>46134</v>
+      </c>
       <c r="D56" s="23" t="s">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="E56" s="18"/>
       <c r="F56" s="20"/>
@@ -3680,14 +3494,14 @@
       <c r="A57" s="12">
         <v>50</v>
       </c>
-      <c r="B57" s="27" t="s">
-        <v>217</v>
+      <c r="B57" s="26" t="s">
+        <v>49</v>
       </c>
       <c r="C57" s="21">
         <v>46135</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="E57" s="18"/>
       <c r="F57" s="20"/>
@@ -3696,10 +3510,12 @@
       <c r="A58" s="12">
         <v>51</v>
       </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="22"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="21">
+        <v>46135</v>
+      </c>
       <c r="D58" s="23" t="s">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="E58" s="18"/>
       <c r="F58" s="20"/>
@@ -3708,10 +3524,12 @@
       <c r="A59" s="12">
         <v>52</v>
       </c>
-      <c r="B59" s="28"/>
-      <c r="C59" s="22"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="21">
+        <v>46135</v>
+      </c>
       <c r="D59" s="23" t="s">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="E59" s="18"/>
       <c r="F59" s="20"/>
@@ -3720,12 +3538,12 @@
       <c r="A60" s="12">
         <v>53</v>
       </c>
-      <c r="B60" s="28"/>
+      <c r="B60" s="27"/>
       <c r="C60" s="21">
         <v>46138</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="E60" s="18"/>
       <c r="F60" s="20"/>
@@ -3734,12 +3552,12 @@
       <c r="A61" s="12">
         <v>54</v>
       </c>
-      <c r="B61" s="28"/>
+      <c r="B61" s="27"/>
       <c r="C61" s="21">
         <v>46138</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="E61" s="18"/>
       <c r="F61" s="20"/>
@@ -3748,12 +3566,12 @@
       <c r="A62" s="12">
         <v>55</v>
       </c>
-      <c r="B62" s="28"/>
+      <c r="B62" s="27"/>
       <c r="C62" s="21">
-        <v>46163</v>
+        <v>46133</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="E62" s="18"/>
       <c r="F62" s="20"/>
@@ -3762,10 +3580,12 @@
       <c r="A63" s="12">
         <v>56</v>
       </c>
-      <c r="B63" s="28"/>
-      <c r="C63" s="22"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="21">
+        <v>46133</v>
+      </c>
       <c r="D63" s="23" t="s">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="E63" s="18"/>
       <c r="F63" s="20"/>
@@ -3774,12 +3594,12 @@
       <c r="A64" s="12">
         <v>57</v>
       </c>
-      <c r="B64" s="29"/>
+      <c r="B64" s="28"/>
       <c r="C64" s="21">
         <v>46149</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>201</v>
+        <v>118</v>
       </c>
       <c r="E64" s="18"/>
       <c r="F64" s="20"/>
@@ -3788,12 +3608,14 @@
       <c r="A65" s="12">
         <v>58</v>
       </c>
-      <c r="B65" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="C65" s="25"/>
+      <c r="B65" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" s="21">
+        <v>46149</v>
+      </c>
       <c r="D65" s="23" t="s">
-        <v>202</v>
+        <v>119</v>
       </c>
       <c r="E65" s="18"/>
       <c r="F65" s="20"/>
@@ -3802,10 +3624,12 @@
       <c r="A66" s="12">
         <v>59</v>
       </c>
-      <c r="B66" s="30"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="21">
+        <v>46149</v>
+      </c>
       <c r="D66" s="23" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="E66" s="18"/>
       <c r="F66" s="20"/>
